--- a/data/raw/GLNPO 2024 Spring/Ontario/D20/Zoops/ON 25 D20 Spring 2024 24GO01I14 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D20/Zoops/ON 25 D20 Spring 2024 24GO01I14 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Zooplankton Counts\Ontario\Spring 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0E1F92-6C9B-4E97-9617-AC75B25AD87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E3913B-F24D-4481-A888-CA21301C70DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{115DA407-9F8E-42B9-A335-5278B2899D20}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{115DA407-9F8E-42B9-A335-5278B2899D20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$168</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3360" r:id="rId2"/>
+    <pivotCache cacheId="49" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -366,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -374,7 +374,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3828,7 +3827,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A7D0135F-81B4-4C9F-B7CC-6384B405E843}" name="PivotTable7" cacheId="3360" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A7D0135F-81B4-4C9F-B7CC-6384B405E843}" name="PivotTable7" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T5:X18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -4262,26 +4261,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262D5C89-422E-45B3-A7DB-B981B8D1F548}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X168"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.7109375" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" customWidth="1"/>
+    <col min="23" max="23" width="3.44140625" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="23" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4678,18 +4678,17 @@
       <c r="T7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7">
         <v>13</v>
       </c>
-      <c r="V7" s="5">
-        <v>19</v>
-      </c>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5">
+      <c r="V7">
+        <v>19</v>
+      </c>
+      <c r="X7">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4744,16 +4743,14 @@
       <c r="T8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8">
         <v>48</v>
       </c>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5">
+      <c r="X8">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4808,18 +4805,17 @@
       <c r="T9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="U9" s="5">
-        <v>1</v>
-      </c>
-      <c r="V9" s="5">
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
         <v>4</v>
       </c>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5">
+      <c r="X9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4874,18 +4870,17 @@
       <c r="T10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10">
         <v>5</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10">
         <v>11</v>
       </c>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5">
+      <c r="X10">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4940,16 +4935,14 @@
       <c r="T11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11">
         <v>35</v>
       </c>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5">
+      <c r="X11">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -5004,16 +4997,14 @@
       <c r="T12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="5">
+      <c r="U12">
         <v>84</v>
       </c>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5">
+      <c r="X12">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5068,18 +5059,17 @@
       <c r="T13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="U13" s="5">
+      <c r="U13">
         <v>11</v>
       </c>
-      <c r="V13" s="5">
+      <c r="V13">
         <v>33</v>
       </c>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5">
+      <c r="X13">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -5134,18 +5124,17 @@
       <c r="T14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" s="5">
+      <c r="V14">
         <v>5</v>
       </c>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5">
+      <c r="X14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -5200,18 +5189,17 @@
       <c r="T15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="U15" s="5">
+      <c r="U15">
         <v>2</v>
       </c>
-      <c r="V15" s="5">
+      <c r="V15">
         <v>3</v>
       </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5">
+      <c r="X15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5266,20 +5254,20 @@
       <c r="T16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="U16" s="5">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="5">
+      <c r="V16">
         <v>0</v>
       </c>
-      <c r="W16" s="5">
-        <v>1</v>
-      </c>
-      <c r="X16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -5334,18 +5322,17 @@
       <c r="T17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="U17" s="5">
+      <c r="U17">
         <v>3</v>
       </c>
-      <c r="V17" s="5">
+      <c r="V17">
         <v>10</v>
       </c>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5">
+      <c r="X17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -5400,20 +5387,20 @@
       <c r="T18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="U18" s="5">
+      <c r="U18">
         <v>202</v>
       </c>
-      <c r="V18" s="5">
+      <c r="V18">
         <v>85</v>
       </c>
-      <c r="W18" s="5">
-        <v>1</v>
-      </c>
-      <c r="X18" s="5">
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
         <v>288</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5466,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5519,7 +5506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5572,7 +5559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5624,13 +5611,13 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="T22" s="8" t="s">
+      <c r="T22" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+    </row>
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5682,17 +5669,17 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="T23" s="8" t="s">
+      <c r="T23" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="U23" s="10" t="s">
+      <c r="U23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="V23" s="9">
+      <c r="V23" s="8">
         <v>0.997</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5744,15 +5731,15 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="T24" s="8"/>
-      <c r="U24" s="10" t="s">
+      <c r="T24" s="7"/>
+      <c r="U24" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="V24" s="9">
+      <c r="V24" s="8">
         <v>1.004</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5804,17 +5791,17 @@
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="T25" s="8" t="s">
+      <c r="T25" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="U25" s="10" t="s">
+      <c r="U25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="V25" s="9">
+      <c r="V25" s="8">
         <v>0.998</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5866,15 +5853,15 @@
       <c r="Q26">
         <v>1</v>
       </c>
-      <c r="T26" s="9"/>
-      <c r="U26" s="10" t="s">
+      <c r="T26" s="8"/>
+      <c r="U26" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="V26" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V26" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5926,15 +5913,15 @@
       <c r="Q27">
         <v>1</v>
       </c>
-      <c r="T27" s="8" t="s">
+      <c r="T27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="U27" s="10" t="s">
+      <c r="U27" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="V27" s="9"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V27" s="8"/>
+    </row>
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5986,15 +5973,15 @@
       <c r="Q28">
         <v>1</v>
       </c>
-      <c r="T28" s="8" t="s">
+      <c r="T28" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="U28" s="9" t="s">
+      <c r="U28" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="V28" s="9"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V28" s="8"/>
+    </row>
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -6046,13 +6033,13 @@
       <c r="Q29">
         <v>1</v>
       </c>
-      <c r="T29" s="8" t="s">
+      <c r="T29" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+    </row>
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -6105,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -6158,7 +6145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -6211,7 +6198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -6264,7 +6251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -6317,7 +6304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6370,7 +6357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6423,7 +6410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6476,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -6529,7 +6516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6582,7 +6569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6635,7 +6622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6688,7 +6675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6741,7 +6728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6794,7 +6781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6847,7 +6834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -6900,7 +6887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6953,7 +6940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -7006,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -7059,7 +7046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -7112,7 +7099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -7165,7 +7152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -7218,7 +7205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -7271,7 +7258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -7324,7 +7311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -7377,7 +7364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7430,7 +7417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7483,7 +7470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7536,7 +7523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7589,7 +7576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7642,7 +7629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7695,7 +7682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7748,7 +7735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7801,7 +7788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7854,7 +7841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7907,7 +7894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7960,7 +7947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -8013,7 +8000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -8066,7 +8053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -8119,7 +8106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -8172,7 +8159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -8225,7 +8212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -8278,7 +8265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -8331,7 +8318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -8384,7 +8371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8437,7 +8424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8490,7 +8477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -8543,7 +8530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8596,7 +8583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8649,7 +8636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8702,7 +8689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8755,7 +8742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8808,7 +8795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8861,7 +8848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8914,7 +8901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8967,7 +8954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -9020,7 +9007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -9073,7 +9060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -9126,7 +9113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -9179,7 +9166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -9232,7 +9219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -9285,7 +9272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -9338,7 +9325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -9391,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9444,7 +9431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9497,7 +9484,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -9550,7 +9537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9603,7 +9590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9656,7 +9643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9709,7 +9696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9762,7 +9749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9815,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9868,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9921,7 +9908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9974,7 +9961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -10027,7 +10014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -10080,7 +10067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -10133,7 +10120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -10186,7 +10173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -10239,7 +10226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -10292,7 +10279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -10345,7 +10332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -10398,7 +10385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10451,7 +10438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10504,7 +10491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -10557,7 +10544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10610,7 +10597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10663,7 +10650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10716,7 +10703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10769,7 +10756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10822,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10875,7 +10862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10928,7 +10915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10981,7 +10968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -11034,7 +11021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -11087,7 +11074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -11140,7 +11127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -11193,7 +11180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -11246,7 +11233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -11299,7 +11286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -11352,7 +11339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11405,7 +11392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11458,7 +11445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11511,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -11564,7 +11551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11617,7 +11604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11670,7 +11657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11723,7 +11710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11776,7 +11763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11829,7 +11816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -11882,7 +11869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -11935,7 +11922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -11988,7 +11975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -12041,7 +12028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -12094,7 +12081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -12147,7 +12134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -12200,7 +12187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -12253,7 +12240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -12306,7 +12293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -12353,13 +12340,13 @@
         <v>28</v>
       </c>
       <c r="P148" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q148">
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -12406,13 +12393,13 @@
         <v>28</v>
       </c>
       <c r="P149" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q149">
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -12465,7 +12452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -12518,7 +12505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -12571,7 +12558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -12624,7 +12611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -12677,7 +12664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -12730,7 +12717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -12783,7 +12770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -12836,7 +12823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -12889,7 +12876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -12942,7 +12929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -12995,7 +12982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -13048,7 +13035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -13101,7 +13088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -13154,7 +13141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -13207,7 +13194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -13260,166 +13247,173 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D166" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E166" s="6" t="s">
+    <row r="166" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D166" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E166" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="5">
         <v>16</v>
       </c>
-      <c r="G166" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H166" s="7" t="s">
+      <c r="G166" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I166" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J166" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K166" s="6" t="s">
+      <c r="I166" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J166" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="L166" s="6" t="s">
+      <c r="L166" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="M166" s="6" t="s">
+      <c r="M166" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N166" s="6" t="s">
+      <c r="N166" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O166" s="6" t="s">
+      <c r="O166" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P166" s="6" t="s">
+      <c r="P166" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q166" s="6">
+      <c r="Q166" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D167" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E167" s="6" t="s">
+    <row r="167" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D167" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E167" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F167" s="6">
+      <c r="F167" s="5">
         <v>16</v>
       </c>
-      <c r="G167" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H167" s="7" t="s">
+      <c r="G167" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H167" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I167" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J167" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K167" s="6" t="s">
+      <c r="I167" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J167" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K167" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L167" s="6" t="s">
+      <c r="L167" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="M167" s="6" t="s">
+      <c r="M167" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N167" s="6" t="s">
+      <c r="N167" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O167" s="6" t="s">
+      <c r="O167" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P167" s="6" t="s">
+      <c r="P167" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q167" s="6">
+      <c r="Q167" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D168" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E168" s="6" t="s">
+    <row r="168" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D168" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E168" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F168" s="6">
+      <c r="F168" s="5">
         <v>8</v>
       </c>
-      <c r="G168" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H168" s="7" t="s">
+      <c r="G168" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I168" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J168" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K168" s="6" t="s">
+      <c r="I168" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K168" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L168" s="6" t="s">
+      <c r="L168" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="M168" s="6" t="s">
+      <c r="M168" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N168" s="6" t="s">
+      <c r="N168" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O168" s="6" t="s">
+      <c r="O168" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P168" s="6" t="s">
+      <c r="P168" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q168" s="6">
+      <c r="Q168" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R168" xr:uid="{262D5C89-422E-45B3-A7DB-B981B8D1F548}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Leptodiaptomus minutus"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
